--- a/artfynd/A 47035-2022 artfynd.xlsx
+++ b/artfynd/A 47035-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ41"/>
+  <dimension ref="A1:AZ50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1359,10 +1359,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>104657329</v>
+        <v>137516937</v>
       </c>
       <c r="B8" t="n">
-        <v>99022</v>
+        <v>99437</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1370,43 +1370,38 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220093</v>
+        <v>219811</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lillviken, Pi lm</t>
+          <t>Arjeplog - Storuman, Pi lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>562912</v>
+        <v>562784</v>
       </c>
       <c r="R8" t="n">
-        <v>7376357</v>
+        <v>7376041</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1433,12 +1428,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-07-10</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-07-10</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1453,31 +1448,31 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Engla Grönvall, Björn Almkvist</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+          <t>C260071 AVK Arjeplog - Storuman</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104657329</t>
+          <t>https://artportalen.se/Sighting/137516937</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2634911</v>
+        <v>104657329</v>
       </c>
       <c r="B9" t="n">
-        <v>99017</v>
+        <v>99022</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1485,37 +1480,46 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219795</v>
+        <v>220093</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sädvajaure, väg 95, NV Guigovaratjah, Pi lm</t>
+          <t>Lillviken, Pi lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>562525</v>
+        <v>562912</v>
       </c>
       <c r="R9" t="n">
-        <v>7377504</v>
+        <v>7376357</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1539,12 +1543,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2012-07-19</t>
+          <t>2022-07-10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2012-07-20</t>
+          <t>2022-07-10</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1555,40 +1559,35 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>vägområde med bäck</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Maj-Lis Granström</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Maj-Lis Granström, Ann-mari Sundkvist</t>
+          <t>Väg och Miljö AB, Engla Grönvall, Björn Almkvist</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>Pite lappmarks flora (2007-2018)</t>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/2634911</t>
+          <t>https://artportalen.se/Sighting/104657329</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>104657323</v>
+        <v>137516278</v>
       </c>
       <c r="B10" t="n">
-        <v>99017</v>
+        <v>99352</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1596,43 +1595,38 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219795</v>
+        <v>219790</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lillviken, Pi lm</t>
+          <t>Arjeplog - Storuman, Pi lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>562334</v>
+        <v>560479</v>
       </c>
       <c r="R10" t="n">
-        <v>7377981</v>
+        <v>7379076</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1659,12 +1653,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2022-07-10</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2022-07-10</t>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>100 tals</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1679,31 +1678,31 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Engla Grönvall, Björn Almkvist</t>
+          <t>Mika Thunell</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+          <t>C260071 AVK Arjeplog - Storuman</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104657323</t>
+          <t>https://artportalen.se/Sighting/137516278</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>104657326</v>
+        <v>2634911</v>
       </c>
       <c r="B11" t="n">
-        <v>99120</v>
+        <v>99017</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1711,46 +1710,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219811</v>
+        <v>219795</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hartm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lillviken, Pi lm</t>
+          <t>Sädvajaure, väg 95, NV Guigovaratjah, Pi lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>562336</v>
+        <v>562525</v>
       </c>
       <c r="R11" t="n">
-        <v>7377983</v>
+        <v>7377504</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1774,12 +1764,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2022-07-10</t>
+          <t>2012-07-19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2022-07-10</t>
+          <t>2012-07-20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1790,35 +1780,40 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>vägområde med bäck</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB</t>
+          <t>Maj-Lis Granström</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Engla Grönvall, Björn Almkvist</t>
+          <t>Maj-Lis Granström, Ann-mari Sundkvist</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+          <t>Pite lappmarks flora (2007-2018)</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104657326</t>
+          <t>https://artportalen.se/Sighting/2634911</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>104657332</v>
+        <v>104657323</v>
       </c>
       <c r="B12" t="n">
-        <v>99120</v>
+        <v>99017</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1826,21 +1821,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219811</v>
+        <v>219795</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1859,10 +1854,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>562345</v>
+        <v>562334</v>
       </c>
       <c r="R12" t="n">
-        <v>7378008</v>
+        <v>7377981</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1924,16 +1919,16 @@
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104657332</t>
+          <t>https://artportalen.se/Sighting/104657323</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>104657350</v>
+        <v>137516282</v>
       </c>
       <c r="B13" t="n">
-        <v>99120</v>
+        <v>99334</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1941,43 +1936,38 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219811</v>
+        <v>219795</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lillviken, Pi lm</t>
+          <t>Arjeplog - Storuman, Pi lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>560655</v>
+        <v>559578</v>
       </c>
       <c r="R13" t="n">
-        <v>7379029</v>
+        <v>7379720</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2004,12 +1994,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2022-07-10</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2022-07-10</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2024,31 +2014,31 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Engla Grönvall, Björn Almkvist</t>
+          <t>Mika Thunell</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+          <t>C260071 AVK Arjeplog - Storuman</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104657350</t>
+          <t>https://artportalen.se/Sighting/137516282</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>2464259</v>
+        <v>104657326</v>
       </c>
       <c r="B14" t="n">
-        <v>99022</v>
+        <v>99120</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2056,37 +2046,46 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220093</v>
+        <v>219811</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Sädvajaure, väg 95, NV Guigovaratjah, Pi lm</t>
+          <t>Lillviken, Pi lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>562348</v>
+        <v>562336</v>
       </c>
       <c r="R14" t="n">
-        <v>7377950</v>
+        <v>7377983</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2110,12 +2109,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2012-07-19</t>
+          <t>2022-07-10</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2012-07-20</t>
+          <t>2022-07-10</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2126,40 +2125,35 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>rik vägkant</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Maj-Lis Granström</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Maj-Lis Granström, Ann-mari Sundkvist</t>
+          <t>Väg och Miljö AB, Engla Grönvall, Björn Almkvist</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>Pite lappmarks flora (2007-2018)</t>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/2464259</t>
+          <t>https://artportalen.se/Sighting/104657326</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>4400315</v>
+        <v>104657332</v>
       </c>
       <c r="B15" t="n">
-        <v>99140</v>
+        <v>99120</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2167,37 +2161,46 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221952</v>
+        <v>219811</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Sädvajaure, väg 95, NV Guigovaratjah, Pi lm</t>
+          <t>Lillviken, Pi lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
         <v>562345</v>
       </c>
       <c r="R15" t="n">
-        <v>7378001</v>
+        <v>7378008</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2221,12 +2224,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2012-07-19</t>
+          <t>2022-07-10</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2012-07-20</t>
+          <t>2022-07-10</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2237,40 +2240,35 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>vägdike med rinnande vatten</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Maj-Lis Granström</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Maj-Lis Granström, Ann-mari Sundkvist</t>
+          <t>Väg och Miljö AB, Engla Grönvall, Björn Almkvist</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>Pite lappmarks flora (2007-2018)</t>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/4400315</t>
+          <t>https://artportalen.se/Sighting/104657332</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>104657322</v>
+        <v>104657350</v>
       </c>
       <c r="B16" t="n">
-        <v>99140</v>
+        <v>99120</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2278,26 +2276,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221952</v>
+        <v>219811</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2311,10 +2309,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>562354</v>
+        <v>560655</v>
       </c>
       <c r="R16" t="n">
-        <v>7377976</v>
+        <v>7379029</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2376,54 +2374,58 @@
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104657322</t>
+          <t>https://artportalen.se/Sighting/104657350</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>4547964</v>
+        <v>137516284</v>
       </c>
       <c r="B17" t="n">
-        <v>98050</v>
+        <v>99437</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222112</v>
+        <v>219811</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Månlåsbräken</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Botrychium lunaria</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Sw.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Sädvajaure, väg 95, NV Guigovaratjah, Pi lm</t>
+          <t>Arjeplog - Storuman, Pi lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>562525</v>
+        <v>559572</v>
       </c>
       <c r="R17" t="n">
-        <v>7377504</v>
+        <v>7379746</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2447,12 +2449,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2012-07-19</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2012-07-20</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2463,40 +2465,35 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>vägområde med bäck</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Maj-Lis Granström</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Maj-Lis Granström, Ann-mari Sundkvist</t>
+          <t>Mika Thunell</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>Pite lappmarks flora (2007-2018)</t>
+          <t>C260071 AVK Arjeplog - Storuman</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/4547964</t>
+          <t>https://artportalen.se/Sighting/137516284</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>4821531</v>
+        <v>137516936</v>
       </c>
       <c r="B18" t="n">
-        <v>104628</v>
+        <v>99437</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2504,37 +2501,41 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222412</v>
+        <v>219811</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Sädvajaure, väg 95, NV Guigovaratjah, Pi lm</t>
+          <t>Arjeplog - Storuman, Pi lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>562525</v>
+        <v>562546</v>
       </c>
       <c r="R18" t="n">
-        <v>7377504</v>
+        <v>7377445</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2558,12 +2559,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2012-07-19</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2012-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2574,40 +2575,35 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>vägområde med bäck</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Maj-Lis Granström</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Maj-Lis Granström, Ann-mari Sundkvist</t>
+          <t>Via Annika Rastén</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>Pite lappmarks flora (2007-2018)</t>
+          <t>C260071 AVK Arjeplog - Storuman</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/4821531</t>
+          <t>https://artportalen.se/Sighting/137516936</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>104657331</v>
+        <v>2464259</v>
       </c>
       <c r="B19" t="n">
-        <v>97982</v>
+        <v>99022</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2615,46 +2611,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222424</v>
+        <v>220093</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fjällummer</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium alpinum</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lillviken, Pi lm</t>
+          <t>Sädvajaure, väg 95, NV Guigovaratjah, Pi lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>561066</v>
+        <v>562348</v>
       </c>
       <c r="R19" t="n">
-        <v>7378896</v>
+        <v>7377950</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2678,12 +2665,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2022-07-10</t>
+          <t>2012-07-19</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2022-07-10</t>
+          <t>2012-07-20</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2694,35 +2681,40 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>rik vägkant</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB</t>
+          <t>Maj-Lis Granström</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Engla Grönvall, Björn Almkvist</t>
+          <t>Maj-Lis Granström, Ann-mari Sundkvist</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+          <t>Pite lappmarks flora (2007-2018)</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104657331</t>
+          <t>https://artportalen.se/Sighting/2464259</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>5988270</v>
+        <v>137516281</v>
       </c>
       <c r="B20" t="n">
-        <v>99038</v>
+        <v>99339</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2730,33 +2722,41 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>223597</v>
+        <v>220093</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Sädvajaure, väg 95, NV Guigovaratjah, Pi lm</t>
+          <t>Arjeplog - Storuman, Pi lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>562348</v>
+        <v>559968</v>
       </c>
       <c r="R20" t="n">
-        <v>7377950</v>
+        <v>7379357</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2780,12 +2780,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2012-07-19</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2012-07-20</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2796,40 +2796,35 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>rik vägkant</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Maj-Lis Granström</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Maj-Lis Granström, Ann-mari Sundkvist</t>
+          <t>Nathalie Edwards</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>Pite lappmarks flora (2007-2018)</t>
+          <t>C260071 AVK Arjeplog - Storuman</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/5988270</t>
+          <t>https://artportalen.se/Sighting/137516281</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>5996034</v>
+        <v>4400315</v>
       </c>
       <c r="B21" t="n">
-        <v>99121</v>
+        <v>99140</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2837,19 +2832,23 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>223614</v>
+        <v>221952</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vanlig brudsporre</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea subsp. conopsea</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2857,10 +2856,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>562348</v>
+        <v>562345</v>
       </c>
       <c r="R21" t="n">
-        <v>7377950</v>
+        <v>7378001</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2906,7 +2905,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>rik vägkant</t>
+          <t>vägdike med rinnande vatten</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2927,16 +2926,16 @@
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/5996034</t>
+          <t>https://artportalen.se/Sighting/4400315</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>6197350</v>
+        <v>104657322</v>
       </c>
       <c r="B22" t="n">
-        <v>97991</v>
+        <v>99140</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2944,34 +2943,43 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>224359</v>
+        <v>221952</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Finnlummer</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum subsp. montellii</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Kukkonen) Karlsson</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Stiehpaltjåhkkås S-sluttning mot Silvervägen, Pi lm</t>
+          <t>Lillviken, Pi lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>561116</v>
+        <v>562354</v>
       </c>
       <c r="R22" t="n">
-        <v>7378866</v>
+        <v>7377976</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2998,17 +3006,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2011-08-22</t>
+          <t>2022-07-10</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2011-08-22</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ganska riklig.</t>
+          <t>2022-07-10</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3020,58 +3023,56 @@
       <c r="AG22" t="b">
         <v>0</v>
       </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>Vägdike</t>
-        </is>
-      </c>
-      <c r="AR22" t="inlineStr"/>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Crister Albinsson</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Crister Albinsson</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr"/>
+          <t>Väg och Miljö AB, Engla Grönvall, Björn Almkvist</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/6197350</t>
+          <t>https://artportalen.se/Sighting/104657322</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>6208559</v>
+        <v>4547964</v>
       </c>
       <c r="B23" t="n">
-        <v>97984</v>
+        <v>98050</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>224362</v>
+        <v>222112</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Nordlummer</t>
+          <t>Månlåsbräken</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. alpestre</t>
+          <t>Botrychium lunaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartm.) Á. Löve &amp; D. Löve</t>
+          <t>(L.) Sw.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3081,10 +3082,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>562348</v>
+        <v>562525</v>
       </c>
       <c r="R23" t="n">
-        <v>7377950</v>
+        <v>7377504</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3130,7 +3131,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>rik vägkant</t>
+          <t>vägområde med bäck</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3151,16 +3152,16 @@
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/6208559</t>
+          <t>https://artportalen.se/Sighting/4547964</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>55262725</v>
+        <v>4821531</v>
       </c>
       <c r="B24" t="n">
-        <v>99120</v>
+        <v>104628</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3168,34 +3169,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219811</v>
+        <v>222412</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Ballasluokta, Pi lm</t>
+          <t>Sädvajaure, väg 95, NV Guigovaratjah, Pi lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>566754</v>
+        <v>562525</v>
       </c>
       <c r="R24" t="n">
-        <v>7375334</v>
+        <v>7377504</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3222,12 +3223,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2015-08-18</t>
+          <t>2012-07-19</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2015-08-18</t>
+          <t>2012-07-20</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3241,33 +3242,37 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Artrik vägslänt</t>
+          <t>vägområde med bäck</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Maj-Lis Granström</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr"/>
+          <t>Maj-Lis Granström, Ann-mari Sundkvist</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Pite lappmarks flora (2007-2018)</t>
+        </is>
+      </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/55262725</t>
+          <t>https://artportalen.se/Sighting/4821531</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>55262745</v>
+        <v>104657331</v>
       </c>
       <c r="B25" t="n">
-        <v>98030</v>
+        <v>97982</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3275,37 +3280,46 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221063</v>
+        <v>222424</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Trådfräken</t>
+          <t>Fjällummer</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Equisetum scirpoides</t>
+          <t>Lycopodium alpinum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Michx.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Ballasluokta, Pi lm</t>
+          <t>Lillviken, Pi lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>566754</v>
+        <v>561066</v>
       </c>
       <c r="R25" t="n">
-        <v>7375334</v>
+        <v>7378896</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3329,12 +3343,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2015-08-18</t>
+          <t>2022-07-10</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2015-08-18</t>
+          <t>2022-07-10</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3345,36 +3359,35 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>Artrik vägslänt</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr"/>
+          <t>Väg och Miljö AB, Engla Grönvall, Björn Almkvist</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/55262745</t>
+          <t>https://artportalen.se/Sighting/104657331</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>55262737</v>
+        <v>5988270</v>
       </c>
       <c r="B26" t="n">
-        <v>97986</v>
+        <v>99038</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3382,34 +3395,30 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221946</v>
+        <v>223597</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Ballasluokta, Pi lm</t>
+          <t>Sädvajaure, väg 95, NV Guigovaratjah, Pi lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>566754</v>
+        <v>562348</v>
       </c>
       <c r="R26" t="n">
-        <v>7375334</v>
+        <v>7377950</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3436,12 +3445,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2015-08-18</t>
+          <t>2012-07-19</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2015-08-18</t>
+          <t>2012-07-20</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3455,33 +3464,37 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Artrik vägslänt</t>
+          <t>rik vägkant</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Maj-Lis Granström</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr"/>
+          <t>Maj-Lis Granström, Ann-mari Sundkvist</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Pite lappmarks flora (2007-2018)</t>
+        </is>
+      </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/55262737</t>
+          <t>https://artportalen.se/Sighting/5988270</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>5268287</v>
+        <v>5996034</v>
       </c>
       <c r="B27" t="n">
-        <v>98234</v>
+        <v>99121</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3489,41 +3502,33 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222759</v>
+        <v>223614</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Taggbräken</t>
+          <t>Vanlig brudsporre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Polystichum lonchitis</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>(L.) Roth</t>
-        </is>
-      </c>
+          <t>Gymnadenia conopsea subsp. conopsea</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Sädvajaure, väg 95, SV Guigovaratjah, Pi lm</t>
+          <t>Sädvajaure, väg 95, NV Guigovaratjah, Pi lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>564442</v>
+        <v>562348</v>
       </c>
       <c r="R27" t="n">
-        <v>7374561</v>
+        <v>7377950</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3561,23 +3566,12 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>vägkant med sprängsten</t>
-        </is>
-      </c>
-      <c r="AP27" t="inlineStr">
-        <is>
-          <t>Umeå-Herbarium UME</t>
-        </is>
-      </c>
-      <c r="AR27" t="inlineStr">
-        <is>
-          <t>12-527</t>
+          <t>rik vägkant</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3598,16 +3592,16 @@
       </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/5268287</t>
+          <t>https://artportalen.se/Sighting/5996034</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>5988022</v>
+        <v>6197350</v>
       </c>
       <c r="B28" t="n">
-        <v>99038</v>
+        <v>97991</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3615,35 +3609,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>223597</v>
+        <v>224359</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Finnlummer</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
+          <t>Lycopodium complanatum subsp. montellii</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Kukkonen) Karlsson</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Väg 95 Arjeplog, Pi lm</t>
+          <t>Stiehpaltjåhkkås S-sluttning mot Silvervägen, Pi lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>566827</v>
+        <v>561116</v>
       </c>
       <c r="R28" t="n">
-        <v>7375325</v>
+        <v>7378866</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3670,12 +3663,17 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2012-07-18</t>
+          <t>2011-08-22</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2012-07-18</t>
+          <t>2011-08-22</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ganska riklig.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3689,37 +3687,34 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Vägkant</t>
-        </is>
-      </c>
+          <t>Vägdike</t>
+        </is>
+      </c>
+      <c r="AR28" t="inlineStr"/>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Maj-Lis Granström</t>
+          <t>Crister Albinsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Maj-Lis Granström</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr">
-        <is>
-          <t>Pite lappmarks flora (2007-2018)</t>
-        </is>
-      </c>
+          <t>Crister Albinsson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/5988022</t>
+          <t>https://artportalen.se/Sighting/6197350</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>55262732</v>
+        <v>6208559</v>
       </c>
       <c r="B29" t="n">
-        <v>99038</v>
+        <v>97984</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3727,30 +3722,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>223597</v>
+        <v>224362</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Nordlummer</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
+          <t>Lycopodium annotinum subsp. alpestre</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Hartm.) Á. Löve &amp; D. Löve</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Ballasluokta, Pi lm</t>
+          <t>Sädvajaure, väg 95, NV Guigovaratjah, Pi lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>566754</v>
+        <v>562348</v>
       </c>
       <c r="R29" t="n">
-        <v>7375334</v>
+        <v>7377950</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3777,12 +3776,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2015-08-18</t>
+          <t>2012-07-19</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2015-08-18</t>
+          <t>2012-07-20</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3796,33 +3795,37 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>Artrik vägslänt</t>
+          <t>rik vägkant</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Maj-Lis Granström</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr"/>
+          <t>Maj-Lis Granström, Ann-mari Sundkvist</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Pite lappmarks flora (2007-2018)</t>
+        </is>
+      </c>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/55262732</t>
+          <t>https://artportalen.se/Sighting/6208559</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>55262731</v>
+        <v>55262725</v>
       </c>
       <c r="B30" t="n">
-        <v>97974</v>
+        <v>99120</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3830,21 +3833,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>224360</v>
+        <v>219811</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gul groddlummer</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Huperzia arctica</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Grossh. ex Tolm.) Sipliv.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3920,16 +3923,16 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/55262731</t>
+          <t>https://artportalen.se/Sighting/55262725</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>2634905</v>
+        <v>137516939</v>
       </c>
       <c r="B31" t="n">
-        <v>99017</v>
+        <v>99437</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3937,39 +3940,38 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>219795</v>
+        <v>219811</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1000</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Väg 95 Ballastviken Arjeplog, Pi lm</t>
+          <t>Arjeplog - Storuman, Pi lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>568829</v>
+        <v>565134</v>
       </c>
       <c r="R31" t="n">
-        <v>7374390</v>
+        <v>7374743</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3996,12 +3998,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2012-07-18</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2012-07-18</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4012,40 +4014,35 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>Vägkant m bäck</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Maj-Lis Granström</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Maj-Lis Granström, Ann-mari Sundkvist</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>Pite lappmarks flora (2007-2018)</t>
+          <t>C260071 AVK Arjeplog - Storuman</t>
         </is>
       </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/2634905</t>
+          <t>https://artportalen.se/Sighting/137516939</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>2463903</v>
+        <v>55262745</v>
       </c>
       <c r="B32" t="n">
-        <v>99022</v>
+        <v>98030</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4053,42 +4050,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220093</v>
+        <v>221063</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Trådfräken</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Equisetum scirpoides</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Väg 95 Arjeplog, Pi lm</t>
+          <t>Ballasluokta, Pi lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>569242</v>
+        <v>566754</v>
       </c>
       <c r="R32" t="n">
-        <v>7373630</v>
+        <v>7375334</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4112,12 +4104,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2012-07-18</t>
+          <t>2015-08-18</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2012-07-18</t>
+          <t>2015-08-18</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4131,34 +4123,30 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>Vägkant m blött dike</t>
+          <t>Artrik vägslänt</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Maj-Lis Granström</t>
+          <t>Sture Westerberg</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Maj-Lis Granström, Ann-mari Sundkvist</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr">
-        <is>
-          <t>Pite lappmarks flora (2007-2018)</t>
-        </is>
-      </c>
+          <t>Sture Westerberg</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/2463903</t>
+          <t>https://artportalen.se/Sighting/55262745</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>4250761</v>
+        <v>55262737</v>
       </c>
       <c r="B33" t="n">
         <v>97986</v>
@@ -4189,17 +4177,17 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Väg 95 Ballastviken Arjeplog, Pi lm</t>
+          <t>Ballasluokta, Pi lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>568829</v>
+        <v>566754</v>
       </c>
       <c r="R33" t="n">
-        <v>7374390</v>
+        <v>7375334</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4223,12 +4211,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2012-07-18</t>
+          <t>2015-08-18</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2012-07-18</t>
+          <t>2015-08-18</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4242,37 +4230,33 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Vägkant m bäck</t>
+          <t>Artrik vägslänt</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Maj-Lis Granström</t>
+          <t>Sture Westerberg</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Maj-Lis Granström, Ann-mari Sundkvist</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr">
-        <is>
-          <t>Pite lappmarks flora (2007-2018)</t>
-        </is>
-      </c>
+          <t>Sture Westerberg</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/4250761</t>
+          <t>https://artportalen.se/Sighting/55262737</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>5996030</v>
+        <v>5268287</v>
       </c>
       <c r="B34" t="n">
-        <v>99121</v>
+        <v>98234</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4280,35 +4264,38 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>223614</v>
+        <v>222759</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vanlig brudsporre</t>
+          <t>Taggbräken</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea subsp. conopsea</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
+          <t>Polystichum lonchitis</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) Roth</t>
+        </is>
+      </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Väg 95 Arjeplog, Pi lm</t>
+          <t>Sädvajaure, väg 95, SV Guigovaratjah, Pi lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>569242</v>
+        <v>564442</v>
       </c>
       <c r="R34" t="n">
-        <v>7373630</v>
+        <v>7374561</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4335,12 +4322,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2012-07-18</t>
+          <t>2012-07-19</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2012-07-18</t>
+          <t>2012-07-20</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4349,12 +4336,23 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>Vägkant m blött dike</t>
+          <t>vägkant med sprängsten</t>
+        </is>
+      </c>
+      <c r="AP34" t="inlineStr">
+        <is>
+          <t>Umeå-Herbarium UME</t>
+        </is>
+      </c>
+      <c r="AR34" t="inlineStr">
+        <is>
+          <t>12-527</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4375,16 +4373,16 @@
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/5996030</t>
+          <t>https://artportalen.se/Sighting/5268287</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>2410666</v>
+        <v>5988022</v>
       </c>
       <c r="B35" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4392,37 +4390,38 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>219790</v>
+        <v>223597</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Sädvajaure, OSO Långudden, Pi lm</t>
+          <t>Väg 95 Arjeplog, Pi lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>575731</v>
+        <v>566827</v>
       </c>
       <c r="R35" t="n">
-        <v>7369800</v>
+        <v>7375325</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4446,12 +4445,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2012-07-19</t>
+          <t>2012-07-18</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2012-07-19</t>
+          <t>2012-07-18</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4465,18 +4464,18 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>vägslänt</t>
+          <t>Vägkant</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Mats G Nettelbladt</t>
+          <t>Maj-Lis Granström</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Mats G Nettelbladt, Charlotte Nordgren</t>
+          <t>Maj-Lis Granström</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4486,16 +4485,16 @@
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/2410666</t>
+          <t>https://artportalen.se/Sighting/5988022</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>2634909</v>
+        <v>55262732</v>
       </c>
       <c r="B36" t="n">
-        <v>99017</v>
+        <v>99038</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4503,34 +4502,30 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>219795</v>
+        <v>223597</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>(L.) Hartm.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Sädvajaure, OSO Långudden, Pi lm</t>
+          <t>Ballasluokta, Pi lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>575667</v>
+        <v>566754</v>
       </c>
       <c r="R36" t="n">
-        <v>7369840</v>
+        <v>7375334</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4557,12 +4552,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2012-07-19</t>
+          <t>2015-08-18</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2012-07-19</t>
+          <t>2015-08-18</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4576,37 +4571,33 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>extremrikkärr, källdråg</t>
+          <t>Artrik vägslänt</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Mats G Nettelbladt</t>
+          <t>Sture Westerberg</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Mats G Nettelbladt, Charlotte Nordgren</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr">
-        <is>
-          <t>Pite lappmarks flora (2007-2018)</t>
-        </is>
-      </c>
+          <t>Sture Westerberg</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/2634909</t>
+          <t>https://artportalen.se/Sighting/55262732</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>104657363</v>
+        <v>55262731</v>
       </c>
       <c r="B37" t="n">
-        <v>99017</v>
+        <v>97974</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4614,46 +4605,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>219795</v>
+        <v>224360</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Gul groddlummer</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Huperzia arctica</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Grossh. ex Tolm.) Sipliv.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>S Lillviken-Jutis, Pi lm</t>
+          <t>Ballasluokta, Pi lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>575724</v>
+        <v>566754</v>
       </c>
       <c r="R37" t="n">
-        <v>7369831</v>
+        <v>7375334</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4677,12 +4659,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2022-07-09</t>
+          <t>2015-08-18</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2022-07-09</t>
+          <t>2015-08-18</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4693,35 +4675,36 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>Artrik vägslänt</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB</t>
+          <t>Sture Westerberg</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Engla Grönvall, Björn Almkvist</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr">
-        <is>
-          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
-        </is>
-      </c>
+          <t>Sture Westerberg</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104657363</t>
+          <t>https://artportalen.se/Sighting/55262731</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>104657354</v>
+        <v>2634905</v>
       </c>
       <c r="B38" t="n">
-        <v>99120</v>
+        <v>99017</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4729,43 +4712,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>219811</v>
+        <v>219795</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(L.) Hartm.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>S Lillviken-Jutis, Pi lm</t>
+          <t>Väg 95 Ballastviken Arjeplog, Pi lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>574579</v>
+        <v>568829</v>
       </c>
       <c r="R38" t="n">
-        <v>7370175</v>
+        <v>7374390</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4792,12 +4771,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2022-07-10</t>
+          <t>2012-07-18</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2022-07-10</t>
+          <t>2012-07-18</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4808,35 +4787,40 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>Vägkant m bäck</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB</t>
+          <t>Maj-Lis Granström</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Engla Grönvall, Björn Almkvist</t>
+          <t>Maj-Lis Granström, Ann-mari Sundkvist</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
-          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+          <t>Pite lappmarks flora (2007-2018)</t>
         </is>
       </c>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104657354</t>
+          <t>https://artportalen.se/Sighting/2634905</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>104657368</v>
+        <v>137516941</v>
       </c>
       <c r="B39" t="n">
-        <v>99120</v>
+        <v>99437</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4863,24 +4847,19 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>S Lillviken-Jutis, Pi lm</t>
+          <t>Arjeplog - Storuman, Pi lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>575804</v>
+        <v>569487</v>
       </c>
       <c r="R39" t="n">
-        <v>7369810</v>
+        <v>7373365</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4907,12 +4886,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2022-07-09</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2022-07-09</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4927,31 +4906,31 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Engla Grönvall, Björn Almkvist</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
-          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+          <t>C260071 AVK Arjeplog - Storuman</t>
         </is>
       </c>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104657368</t>
+          <t>https://artportalen.se/Sighting/137516941</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>17319711</v>
+        <v>2463903</v>
       </c>
       <c r="B40" t="n">
-        <v>106229</v>
+        <v>99022</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4959,40 +4938,42 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221725</v>
+        <v>220093</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Riebrebuoda vid väg 95, Silvervägen, Pi lm</t>
+          <t>Väg 95 Arjeplog, Pi lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>573926</v>
+        <v>569242</v>
       </c>
       <c r="R40" t="n">
-        <v>7370689</v>
+        <v>7373630</v>
       </c>
       <c r="S40" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5016,12 +4997,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2014-07-04</t>
+          <t>2012-07-18</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2014-07-04</t>
+          <t>2012-07-18</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5032,16 +5013,21 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>Vägkant m blött dike</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Elisabet Arvidson</t>
+          <t>Maj-Lis Granström</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Elisabet Arvidson, Börje Törnberg</t>
+          <t>Maj-Lis Granström, Ann-mari Sundkvist</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -5051,16 +5037,16 @@
       </c>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/17319711</t>
+          <t>https://artportalen.se/Sighting/2463903</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>17319708</v>
+        <v>4250761</v>
       </c>
       <c r="B41" t="n">
-        <v>104628</v>
+        <v>97986</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5068,16 +5054,16 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>222412</v>
+        <v>221946</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -5086,22 +5072,19 @@
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Riebrebuoda vid väg 95, Silvervägen, Pi lm</t>
+          <t>Väg 95 Ballastviken Arjeplog, Pi lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>573926</v>
+        <v>568829</v>
       </c>
       <c r="R41" t="n">
-        <v>7370689</v>
+        <v>7374390</v>
       </c>
       <c r="S41" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5125,12 +5108,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2014-07-04</t>
+          <t>2012-07-18</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2014-07-04</t>
+          <t>2012-07-18</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5141,24 +5124,1036 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>Vägkant m bäck</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
+          <t>Maj-Lis Granström</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Maj-Lis Granström, Ann-mari Sundkvist</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>Pite lappmarks flora (2007-2018)</t>
+        </is>
+      </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4250761</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>137516943</v>
+      </c>
+      <c r="B42" t="n">
+        <v>98364</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>222112</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Månlåsbräken</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Botrychium lunaria</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) Sw.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Arjeplog - Storuman, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>569503</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7373333</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Arvid de Jong</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>C260071 AVK Arjeplog - Storuman</t>
+        </is>
+      </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137516943</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>5996030</v>
+      </c>
+      <c r="B43" t="n">
+        <v>99121</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>223614</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Vanlig brudsporre</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea subsp. conopsea</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Väg 95 Arjeplog, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>569242</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7373630</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2012-07-18</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2012-07-18</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>Vägkant m blött dike</t>
+        </is>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Maj-Lis Granström</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Maj-Lis Granström, Ann-mari Sundkvist</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>Pite lappmarks flora (2007-2018)</t>
+        </is>
+      </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5996030</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>2410666</v>
+      </c>
+      <c r="B44" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Sädvajaure, OSO Långudden, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>575731</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7369800</v>
+      </c>
+      <c r="S44" t="n">
+        <v>25</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2012-07-19</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2012-07-19</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>vägslänt</t>
+        </is>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Mats G Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Mats G Nettelbladt, Charlotte Nordgren</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>Pite lappmarks flora (2007-2018)</t>
+        </is>
+      </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2410666</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>2634909</v>
+      </c>
+      <c r="B45" t="n">
+        <v>99017</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>219795</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Grönkulla</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Coeloglossum viride</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) Hartm.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Sädvajaure, OSO Långudden, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>575667</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7369840</v>
+      </c>
+      <c r="S45" t="n">
+        <v>25</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2012-07-19</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2012-07-19</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>extremrikkärr, källdråg</t>
+        </is>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Mats G Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Mats G Nettelbladt, Charlotte Nordgren</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>Pite lappmarks flora (2007-2018)</t>
+        </is>
+      </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2634909</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>104657363</v>
+      </c>
+      <c r="B46" t="n">
+        <v>99017</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>219795</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Grönkulla</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Coeloglossum viride</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) Hartm.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>S Lillviken-Jutis, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>575724</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7369831</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2022-07-09</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2022-07-09</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Engla Grönvall, Björn Almkvist</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104657363</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>104657354</v>
+      </c>
+      <c r="B47" t="n">
+        <v>99120</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>S Lillviken-Jutis, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>574579</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7370175</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2022-07-10</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2022-07-10</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Engla Grönvall, Björn Almkvist</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104657354</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>104657368</v>
+      </c>
+      <c r="B48" t="n">
+        <v>99120</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>S Lillviken-Jutis, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>575804</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7369810</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2022-07-09</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2022-07-09</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Engla Grönvall, Björn Almkvist</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104657368</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>17319711</v>
+      </c>
+      <c r="B49" t="n">
+        <v>106229</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Riebrebuoda vid väg 95, Silvervägen, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>573926</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7370689</v>
+      </c>
+      <c r="S49" t="n">
+        <v>25</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2014-07-04</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2014-07-04</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
           <t>Elisabet Arvidson</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
+      <c r="AX49" t="inlineStr">
         <is>
           <t>Elisabet Arvidson, Börje Törnberg</t>
         </is>
       </c>
-      <c r="AY41" t="inlineStr">
+      <c r="AY49" t="inlineStr">
         <is>
           <t>Pite lappmarks flora (2007-2018)</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17319711</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>17319708</v>
+      </c>
+      <c r="B50" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Riebrebuoda vid väg 95, Silvervägen, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>573926</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7370689</v>
+      </c>
+      <c r="S50" t="n">
+        <v>25</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2014-07-04</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2014-07-04</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Elisabet Arvidson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Elisabet Arvidson, Börje Törnberg</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t>Pite lappmarks flora (2007-2018)</t>
+        </is>
+      </c>
+      <c r="AZ50" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/17319708</t>
         </is>
@@ -5206,6 +6201,15 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 47035-2022 artfynd.xlsx
+++ b/artfynd/A 47035-2022 artfynd.xlsx
@@ -1362,7 +1362,7 @@
         <v>137516937</v>
       </c>
       <c r="B8" t="n">
-        <v>99437</v>
+        <v>99440</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>137516278</v>
       </c>
       <c r="B10" t="n">
-        <v>99352</v>
+        <v>99355</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>137516282</v>
       </c>
       <c r="B13" t="n">
-        <v>99334</v>
+        <v>99337</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>137516284</v>
       </c>
       <c r="B17" t="n">
-        <v>99437</v>
+        <v>99440</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         <v>137516936</v>
       </c>
       <c r="B18" t="n">
-        <v>99437</v>
+        <v>99440</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
         <v>137516281</v>
       </c>
       <c r="B20" t="n">
-        <v>99339</v>
+        <v>99342</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3932,7 +3932,7 @@
         <v>137516939</v>
       </c>
       <c r="B31" t="n">
-        <v>99437</v>
+        <v>99440</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4820,7 +4820,7 @@
         <v>137516941</v>
       </c>
       <c r="B39" t="n">
-        <v>99437</v>
+        <v>99440</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5157,7 +5157,7 @@
         <v>137516943</v>
       </c>
       <c r="B42" t="n">
-        <v>98364</v>
+        <v>98367</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
